--- a/Indomie Clients Details/Rainbow/Rainbow BT.xlsx
+++ b/Indomie Clients Details/Rainbow/Rainbow BT.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73A109E-AA3F-413D-ADCC-91129007EFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A355B62-34A8-4E8D-8D17-F104E699A7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3382,7 +3382,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3410,7 +3410,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4625,7 +4625,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4653,7 +4653,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5868,7 +5868,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5896,7 +5896,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7111,7 +7111,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7139,7 +7139,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8354,7 +8354,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8382,7 +8382,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9597,7 +9597,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9625,7 +9625,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10840,7 +10840,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10868,7 +10868,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12083,7 +12083,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12111,7 +12111,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13326,7 +13326,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13354,7 +13354,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14569,7 +14569,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14597,7 +14597,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18562,7 +18562,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18590,7 +18590,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19802,7 +19802,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19830,7 +19830,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21041,7 +21041,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21069,7 +21069,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22280,7 +22280,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22308,7 +22308,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23524,7 +23524,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23552,7 +23552,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>35561.741193540001</v>
+        <v>31029.347591640002</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23997,15 +23997,15 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>4406.8499999999995</v>
+        <v>0</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="171">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -24013,23 +24013,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>616.95899999999995</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>3789.8909999999996</v>
+        <v>0</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>719.95337999999992</v>
+        <v>0</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>22.549221899999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>4532.3936018999993</v>
+        <v>0</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24467,7 +24467,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>13.65</v>
+        <v>11.55</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24478,15 +24478,15 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>546</v>
+        <v>462</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>34576.71</v>
+        <v>30169.86</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
@@ -24494,23 +24494,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>4840.7394000000004</v>
+        <v>4223.7804000000006</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>29735.970600000001</v>
+        <v>25946.079599999997</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>5648.8465079999996</v>
+        <v>4928.8931279999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>176.92408553999999</v>
+        <v>154.37486364</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>35561.741193540001</v>
+        <v>31029.347591639998</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24718,7 +24718,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>35561.741193540001</v>
+        <v>31029.347591640002</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24751,7 +24751,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>34576.71</v>
+        <v>30169.86</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24772,7 +24772,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>4840.7394000000004</v>
+        <v>4223.7804000000006</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24815,7 +24815,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>29735.970600000001</v>
+        <v>25946.079600000001</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24840,7 +24840,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>5648.8465079999996</v>
+        <v>4928.8931279999997</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24862,7 +24862,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>35384.817108000003</v>
+        <v>30874.972728000001</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>884.62042770000016</v>
+        <v>771.87431820000006</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24897,7 +24897,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>36269.437535700003</v>
+        <v>31646.8470462</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25069,7 +25069,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25097,7 +25097,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25518,38 +25518,36 @@
       </c>
       <c r="G18" s="113"/>
       <c r="H18" s="114">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>4406.8499999999995</v>
-      </c>
-      <c r="J18" s="116">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="116"/>
       <c r="K18" s="1">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>616.95899999999995</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>3789.8909999999996</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>719.95337999999992</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>22.549221899999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>4532.3936018999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25915,15 +25913,15 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>546</v>
+        <v>462</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>34576.71</v>
+        <v>30169.86</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
@@ -25931,23 +25929,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>4840.7394000000004</v>
+        <v>4223.7804000000006</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>29735.970600000001</v>
+        <v>25946.079599999997</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>5648.8465079999996</v>
+        <v>4928.8931279999997</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>176.92408553999999</v>
+        <v>154.37486364</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>35561.741193540001</v>
+        <v>31029.347591639998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25997,7 +25995,7 @@
       <c r="O28" s="223"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>34576.71</v>
+        <v>30169.86</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26018,7 +26016,7 @@
       <c r="O29" s="225"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>4840.7394000000004</v>
+        <v>4223.7804000000006</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26061,7 +26059,7 @@
       <c r="O31" s="225"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>29735.970600000001</v>
+        <v>25946.079600000001</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26086,7 +26084,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>5648.8465079999996</v>
+        <v>4928.8931279999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26108,7 +26106,7 @@
       <c r="O33" s="227"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>35384.817108000003</v>
+        <v>30874.972728000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26133,7 +26131,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>176.92408554000002</v>
+        <v>154.37486364</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26143,7 +26141,7 @@
       <c r="O35" s="205"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>35561.741193540001</v>
+        <v>31029.347591640002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26315,7 +26313,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26343,7 +26341,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27558,7 +27556,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27586,7 +27584,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28800,7 +28798,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28828,7 +28826,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30043,7 +30041,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30071,7 +30069,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31287,7 +31285,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31315,7 +31313,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
